--- a/wc2024227/drafts/out/WC2024227_Master_Evidence_Chronology_20260808.xlsx
+++ b/wc2024227/drafts/out/WC2024227_Master_Evidence_Chronology_20260808.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOCUMENT SCHEDULE" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISSUE MAP (INTERNAL)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEGEND &amp; SOURCES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RISK REGISTER (INTERNAL)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'MASTER CHRONOLOGY'!$1:$1</definedName>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +75,26 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="009C5700"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001F3864"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,6 +204,23 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -744,7 +782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2780,6 +2818,158 @@
       <c r="J41" s="11" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>C-041</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>7:09 PM</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>Reply to Reese (contains 'misuse of authority'; 'ethical unit' reference)</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>Reese</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H42" s="19" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I42" s="19" t="inlineStr">
+        <is>
+          <t>FRMS disclosure</t>
+        </is>
+      </c>
+      <c r="J42" s="19" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>C-042</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>1:28 PM</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>Self-note 'issues' (contains 'knowingly defrauds the department'; attendance comments)</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
+          <t>Email (self)</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>pack 02 p.166</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>C-043</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr"/>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>Draft reply to abandonment letter (contains 'wage theft'/'coerced'; CCC reference)</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
+        <is>
+          <t>(draft)</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H44" s="19" t="inlineStr">
+        <is>
+          <t>Draft — sent? verify</t>
+        </is>
+      </c>
+      <c r="I44" s="19" t="inlineStr">
+        <is>
+          <t>2024-10-09 draft</t>
+        </is>
+      </c>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>Held (draft)</t>
         </is>
       </c>
     </row>
@@ -3712,4 +3902,277 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>⛔ INTERNAL — HIS OWN ADVERSE MATERIAL. The RESPONDENT holds these. Do NOT delete or hide the documents; PREPARE them. This sheet is prep — do NOT disclose this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>His own statement / document</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>What is damaging</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>Where it appears</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>Handling (own it — never hide)</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>'Chloe knowingly defrauds the department' (18 May self-note)</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>Imports FRAUD (rule 2); opens s 32(5)(b) perception</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>pack 02 p.166 (disclosed)</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>In regardless. NON-ADOPT. If raised: lay expression of frustration re unworked hours, NOT an allegation of criminal fraud; redirect to conduct; note same email says 'not done with malintent'</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="inlineStr">
+        <is>
+          <t>'I used the word loosely; I press no allegation of fraud.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>'misuse of authority' (15 May 7:09pm reply)</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Reads combative / motive</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>FRMS disclosure</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Reactive to the retraction; do not lead with it; if raised, it was a response to being told to withdraw a reasonable request</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>Say nothing unless raised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>R-03</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>'forwarded to the ethical unit for investigation' (15 May reply)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Ties email to PID/reprisal track</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>FRMS disclosure</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>Do not amplify. It is simply the fact a protected disclosure was on foot. Manner point stands without it</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>Do not repeat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>R-04</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>'wage theft' / 'coerced' / 'purposely delayed' + CCC reference (9 Oct 2024 DRAFT)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Fraud/criminal framing (rules 1-2)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>2024-10-09 draft reply</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>⚠ VERIFY IF SENT. If never sent, it is a draft only. The FACTS in it are usable; the characterisations are NOT</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Never adopt 'wage theft'/'coerced'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>'combative' characterisation (he is answering it)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Employer's label of him</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>corpus (his reply)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>His measured reply rebuts it. Do not re-argue; the documents show a values-based request</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Let the email answer it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>'Chloe and Tammy contributed to my injury — I will distance myself' (to Amy Mo)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>His PERCEPTION of causation → s 32(5)(b) magnet</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>corpus pack 10</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Fine as his account to WorkCover; do NOT build causation on his perception. Injury = conditions, per the report</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Causation is the doctor's, not his opinion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>⛔ SEPARATE CATEGORY — NOT IN THIS WORKBOOK: the QPS/PPN/strike-out/separation-document items (CLAUDE.md rule 10) are the personal/QPS file. They are NOT part of the WC record and are never entered here or voiced. Do not add them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>PRINCIPLE (Briginshaw): the appellant carries the onus. A witness who hides adverse material loses credibility on EVERYTHING. Owning your own bad documents — and having the handling ready — is how you stay the reliable narrator. In evidence ≠ adopted.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A10:F10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/wc2024227/drafts/out/WC2024227_Master_Evidence_Chronology_20260808.xlsx
+++ b/wc2024227/drafts/out/WC2024227_Master_Evidence_Chronology_20260808.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,6 +95,10 @@
     <font>
       <i val="1"/>
       <color rgb="001F3864"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -166,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -221,6 +225,15 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -782,7 +795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2970,6 +2983,298 @@
       <c r="J44" s="19" t="inlineStr">
         <is>
           <t>Held (draft)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>C-044</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr"/>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>Clinical entries — anxiety / ADHD (relied on for 'pre-existing')</t>
+        </is>
+      </c>
+      <c r="E45" s="26" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="F45" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H45" s="26" t="inlineStr">
+        <is>
+          <t>Medical</t>
+        </is>
+      </c>
+      <c r="I45" s="26" t="inlineStr">
+        <is>
+          <t>SOFC ¶8; Form 24 ¶32</t>
+        </is>
+      </c>
+      <c r="J45" s="26" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>C-045</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr"/>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>QSuper income-protection report (A4) — 'complete incapacity'; names competing life stressors</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>Dr Krishnaiah</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="inlineStr">
+        <is>
+          <t>QSuper</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H46" s="26" t="inlineStr">
+        <is>
+          <t>Medical</t>
+        </is>
+      </c>
+      <c r="I46" s="26" t="inlineStr">
+        <is>
+          <t>2025-02-13 report</t>
+        </is>
+      </c>
+      <c r="J46" s="26" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>C-046</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr"/>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>Reinstatement process thread</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>J. Roberts</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H47" s="26" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="inlineStr">
+        <is>
+          <t>pack 05</t>
+        </is>
+      </c>
+      <c r="J47" s="26" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>C-047</t>
+        </is>
+      </c>
+      <c r="B48" s="26" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr"/>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>Attendance letter — '34 occasions'</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>S. Hughes</t>
+        </is>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H48" s="26" t="inlineStr">
+        <is>
+          <t>Letter</t>
+        </is>
+      </c>
+      <c r="I48" s="26" t="inlineStr">
+        <is>
+          <t>AttF (32pp)</t>
+        </is>
+      </c>
+      <c r="J48" s="26" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>C-048</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>11:43 AM</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>Request for Medical Information (9 questions)</t>
+        </is>
+      </c>
+      <c r="E49" s="26" t="inlineStr">
+        <is>
+          <t>S. Hughes</t>
+        </is>
+      </c>
+      <c r="F49" s="26" t="inlineStr">
+        <is>
+          <t>Dr Ma</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H49" s="26" t="inlineStr">
+        <is>
+          <t>Letter</t>
+        </is>
+      </c>
+      <c r="I49" s="26" t="inlineStr">
+        <is>
+          <t>RFMI</t>
+        </is>
+      </c>
+      <c r="J49" s="26" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>C-049</t>
+        </is>
+      </c>
+      <c r="B50" s="26" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr"/>
+      <c r="D50" s="26" t="inlineStr">
+        <is>
+          <t>Psychiatric consultation — Report A / Report B</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
+        <is>
+          <t>Psychiatrist</t>
+        </is>
+      </c>
+      <c r="F50" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H50" s="26" t="inlineStr">
+        <is>
+          <t>Medical</t>
+        </is>
+      </c>
+      <c r="I50" s="26" t="inlineStr">
+        <is>
+          <t>(scheduled)</t>
+        </is>
+      </c>
+      <c r="J50" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3910,7 +4215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4152,15 +4457,177 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>QSuper/Krishnaiah report 13 Feb 2025 (A4): 'complete incapacity'; competing causes (bereavement, relationship breakdown, job loss); ADHD/Vyvanse; litigation framed as symptom</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>THE biggest medical adverse doc. Competing causes; incapacity; ADHD; 'extensive researching consumed his whole life'</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>2025-02-13 report (held; in the record)</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>It is an income-protection CAPACITY report, not a s 32(1) causation opinion. 'Complete incapacity' was accurate on the day (he had been dismissed, no income). Competing causes must be NAMED and WEIGHED by the 12 Aug psychiatrist, not omitted. 'Job loss' = the employer's own act, reversed</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="inlineStr">
+        <is>
+          <t>'The report answered capacity, not causation; the June 2024 causation question is the psychiatrist's.'</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>R-08</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>26 Oct 2022 anxiety/ADHD entries</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Pre-existing condition (SOFC ¶8; Form 24 ¶32)</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>medical records</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>s 32(3)(b): aggravation of a pre-existing condition IS an injury; employment need only be a significant contributor to the aggravation. Hawes: 'no pre-existing factor or condition'</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>'Aggravation is an injury; employment is a significant contributing factor to it.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>8 Sep 2025 Hughes attendance letter — '34 occasions' (32pp, no text layer)</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Biggest RISK document. Attendance history; the 25/26 June adjacency</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>AttF</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>Employment track, post-injury. G3 asymmetry (treated as conduct, not medical). NEVER run the 25/26 June adjacency as if it does not exist. Do NOT volunteer</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>Handle only if raised; keep to the G3-asymmetry frame.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Competing life stressors named in the medical (bereavement; relationship breakdown; job loss)</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>s 32(1) — competing NON-work causes</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>A4 / medical</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Named and weighed in Report B, not hidden. Employment need only be A significant contributor (not THE cause). Job loss = employer's act</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>'Employment need only be a significant contributor, and it was.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>R-11</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Personal crisis / separation references (his own emails) + DFV material</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>⚠ SENSITIVE. Competing-cause + personal exposure</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>corpus; 2025-hughes-history AttA-D (NOT opened)</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>⛔ DO NOT mine or detail without Cory's instruction. The DFV AttA-D are deliberately unopened. The QPS/PPN/separation (rule 10) items are a SEPARATE file and NEVER entered/voiced. Decide WITH Cory what, if anything, the psychiatrist is told for competing-cause completeness</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>TAKE INSTRUCTIONS — do not act unilaterally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>⛔ SEPARATE CATEGORY — NOT IN THIS WORKBOOK: the QPS/PPN/strike-out/separation-document items (CLAUDE.md rule 10) are the personal/QPS file. They are NOT part of the WC record and are never entered here or voiced. Do not add them.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>PRINCIPLE (Briginshaw): the appellant carries the onus. A witness who hides adverse material loses credibility on EVERYTHING. Owning your own bad documents — and having the handling ready — is how you stay the reliable narrator. In evidence ≠ adopted.</t>
         </is>

--- a/wc2024227/drafts/out/WC2024227_Master_Evidence_Chronology_20260808.xlsx
+++ b/wc2024227/drafts/out/WC2024227_Master_Evidence_Chronology_20260808.xlsx
@@ -144,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -166,11 +166,55 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -234,6 +278,8 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4480,12 +4526,12 @@
       </c>
       <c r="E9" s="27" t="inlineStr">
         <is>
-          <t>It is an income-protection CAPACITY report, not a s 32(1) causation opinion. 'Complete incapacity' was accurate on the day (he had been dismissed, no income). Competing causes must be NAMED and WEIGHED by the 12 Aug psychiatrist, not omitted. 'Job loss' = the employer's own act, reversed</t>
+          <t>It is a QSuper INCOME-PROTECTION report, expressly 'NOT for medico-legal use' (its own header) — not a s 32(1) causation opinion. Taken ~7 months post-injury (consult ~Jan 2025, report 13 Feb). The competing causes sit at DIFFERENT times: 'job loss' = the Oct 2024 dismissal (post-injury, employer's act); the separation ~6 months later (post-injury) cannot have caused the June 2024 injury. 'Complete incapacity' = a later compounded state (dismissed, no income); he returned 24 Feb struggling. Report B answers causation at June 2024 — a different question at a different time.</t>
         </is>
       </c>
       <c r="F9" s="27" t="inlineStr">
         <is>
-          <t>'The report answered capacity, not causation; the June 2024 causation question is the psychiatrist's.'</t>
+          <t>'The report answered QSuper capacity in early 2025, not causation in June 2024; the later stressors post-date the injury.'</t>
         </is>
       </c>
     </row>
@@ -4495,31 +4541,11 @@
           <t>R-08</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
-        <is>
-          <t>26 Oct 2022 anxiety/ADHD entries</t>
-        </is>
-      </c>
-      <c r="C10" s="28" t="inlineStr">
-        <is>
-          <t>Pre-existing condition (SOFC ¶8; Form 24 ¶32)</t>
-        </is>
-      </c>
-      <c r="D10" s="28" t="inlineStr">
-        <is>
-          <t>medical records</t>
-        </is>
-      </c>
-      <c r="E10" s="28" t="inlineStr">
-        <is>
-          <t>s 32(3)(b): aggravation of a pre-existing condition IS an injury; employment need only be a significant contributor to the aggravation. Hawes: 'no pre-existing factor or condition'</t>
-        </is>
-      </c>
-      <c r="F10" s="28" t="inlineStr">
-        <is>
-          <t>'Aggravation is an injury; employment is a significant contributing factor to it.'</t>
-        </is>
-      </c>
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="30" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
@@ -4559,31 +4585,11 @@
           <t>R-10</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>Competing life stressors named in the medical (bereavement; relationship breakdown; job loss)</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>s 32(1) — competing NON-work causes</t>
-        </is>
-      </c>
-      <c r="D12" s="28" t="inlineStr">
-        <is>
-          <t>A4 / medical</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t>Named and weighed in Report B, not hidden. Employment need only be A significant contributor (not THE cause). Job loss = employer's act</t>
-        </is>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>'Employment need only be a significant contributor, and it was.'</t>
-        </is>
-      </c>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="30" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
